--- a/reports/meta_intel_2026-W20.xlsx
+++ b/reports/meta_intel_2026-W20.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-12 11:56 UTC</t>
+          <t>Generated: 2026-05-15 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>123</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -500,7 +500,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -527,27 +527,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Meminto</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Storykeeper</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -557,17 +557,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Keepsake</t>
+          <t>Remento</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Enna</t>
+          <t>Keepsake</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -577,17 +577,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>StoryWorth</t>
+          <t>Meminto</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tell me</t>
+          <t>StoryWorth</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -597,7 +597,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HereAfter AI</t>
+          <t>Tellmel</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -607,10 +607,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>HereAfter AI</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>No Story Lost</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Heritage Whisper</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -625,12 +665,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -700,7 +740,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25732574163013261</t>
+          <t>944701718393132</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -720,20 +760,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -745,7 +780,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4226979260924443</t>
+          <t>1960998354553609</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -755,30 +790,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>I decided I wasn't going to miss the chance to ask so many more questions... Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -790,7 +825,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1500465744970742</t>
+          <t>982542424313716</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -810,11 +845,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -830,7 +865,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2869974503345418</t>
+          <t>4525953724345514</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -840,21 +875,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Looking for an easy but meaningful gift? Remento makes it simple to capture your mom’s stories and turn them into something lasting. Take advantage of our Mother’s Day offer and get started today.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Don't Let Mom's Story Fade</t>
+          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -870,7 +900,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>761678472864497</t>
+          <t>1501005738186114</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -880,25 +910,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No typing. No passwords. No tech stress.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -910,7 +940,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1158907893071435</t>
+          <t>940930155514923</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,30 +950,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
+          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -955,7 +975,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1288732889525790</t>
+          <t>1985079728773317</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -965,25 +985,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -995,7 +1010,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1555381445360883</t>
+          <t>4435145500031851</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1005,30 +1020,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Con Remento, preservar historias valiosas es tan fácil como tener una conversación. Ellos simplemente hablan, y Remento hace el resto: convierte sus palabras en historias escritas profesionalmente. Cada historia incluye un código QR que, al escanearlo, te lleva a las grabaciones originales. Así puedes verlos o escucharlos cuando quieras, contándote su historia. 👆 Elige preguntas o fotos para inspirar las historias 📱 Graba las respuestas habladas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>📖 Remento convierte las grabaciones en un libro lleno de historias escritas</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1050,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>712538008277944</t>
+          <t>4305501549596110</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1050,30 +1060,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Introducing the autobiography that talks back! Family can scan each page to hear your recording! 80% of life story books never get made, because the process requires so much writing &amp; typing. So get Remento and actually make history for your family. "My kids see their grandparents as heroes now!" - Karen L.</t>
+          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The AI Biographer &amp; Book are only $99!</t>
+          <t>📖 Remento turns recordings into a book of written stories</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>763892383471439</t>
+          <t>1701124344229972</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1095,30 +1100,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Introducing the autobiography that talks back! Family can scan each page to hear your recording! 80% of life story books never get made, because the process requires so much writing &amp; typing. So get Remento and actually make history for your family. "My kids see their grandparents as heroes now!" - Karen L.</t>
+          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The AI Biographer &amp; Book are only $99!</t>
+          <t>No typing. No passwords. No tech stress.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2025-12-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>136</v>
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1130,40 +1130,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1601908867660679</t>
+          <t>852962227868306</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>IG mamadefour with Remento</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
+          <t>Todos tenemos historias que merecen ser contadas… y ahora pueden vivir para siempre. Le regalé a mi papá algo único: su propio libro de memorias hecho con @getremento. Remento aparecio en Shark Tank y funciona asi, te manda preguntas, grabás tus respuestas en video, y la plataforma convierte esa grabación en texto automáticamente.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1165,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1284057377054392</t>
+          <t>1639743033742217</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1185,25 +1175,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Everyone loves stories. Preserving your family's stories shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1215,35 +1200,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>773271491707229</t>
+          <t>1282383093577411</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Actor Cara AnnMarie with Remento</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>For only $99 you get: 📝 No-Write Biographer Service 📘 Hardcover Memoir (in color!)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>🧠 Digital Family Memory Hub</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1240,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1485515746687783</t>
+          <t>2028325661366433</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Actor Cara AnnMarie with Remento</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>This Mother's Day, give Mom the ultimate gift: her story. • 80% of life stories never get told because they're too hard to write. Remento makes it easy! Get an interactive book that captures</t>
+          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>her timeless tales for your whole family.</t>
+          <t>No typing. No passwords. No tech stress.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1290,2441 +1275,2321 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1201803034706600</t>
+          <t>1868277354563662</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>816389671445707</t>
+          <t>1362684515702149</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>725689447110382</t>
+          <t>1938930663325095</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2306815973153192</t>
+          <t>1852060685669387</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>189</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>669776749497675</t>
+          <t>1296748252140081</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>189</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1259749095777072</t>
+          <t>841302105060560</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2036001257171394</t>
+          <t>3976129939359406</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>854656737028819</t>
+          <t>1588345672369492</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1762415531013839</t>
+          <t>1177236264536592</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>144</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2199250597166640</t>
+          <t>1943193019573119</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>See why Tim Ferris picked Remento for his mom: "Worked better than could have hoped, A+ investment!" Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. 80% of life story books never get made, because the process requires so much writing &amp; typing. So get Remento and actually make history for your family.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>"My kids see their grandparents as heroes now!"</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2025-07-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>189</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>706731428898675</t>
+          <t>4072587919646468</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1051096066991449</t>
+          <t>2260190851070799</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1386013609706717</t>
+          <t>966816482430409</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Care Partner Patti with Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>I would give anything to hear my Mama share her childhood memories, our favorite moments together as a family, and to hear her say my name. That’s why capturing voices matters so much to me. Not just memories… but the sound of the people we love. @getremento makes it possible to save those voices — the stories, the laughter, the love — while we still can.</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1535564994261659</t>
+          <t>1630159098158899</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>144</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>759002970126462</t>
+          <t>796404973298946</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>15</v>
+        <v>189</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4102209836591932</t>
+          <t>3727759467519562</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>732231183253991</t>
+          <t>933151279692839</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1133290715187557</t>
+          <t>850477457839087</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Introducing the autobiography that talks back! The AI Biographer &amp; Book: Only $99</t>
+          <t>Mach Oma &amp; Opa glücklich!🫶 ➡️ Jetzt 120€ sparen! (Gilt nur für kurze Zeit) Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The AI Biographer &amp; Book: Only $99</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>843515291838326</t>
+          <t>1549478262721918</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1555908845587683</t>
+          <t>2040130603507445</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2108461359889159</t>
+          <t>1171548231746967</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Elliekeepsbusy with Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>31</v>
+        <v>181</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>836067402395580</t>
+          <t>871339118687590</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UGC With Van with Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>I gifted my family my grandparent's VOICE.</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3083201511858451</t>
+          <t>26604726072519208</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1256090386361152</t>
+          <t>2761672647588250</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kristen Coffield with Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Grandparents don’t need more sweaters or socks or gadgets this holiday! 🙅🎄🎁 For years I kept promising myself I would go through the boxes of photos in the attic. You know, create gift albums to tell the story of our lives. Guess what? That’s probably not going to happen. But what I have started doing is much easier and more impactful.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>938872095381748</t>
+          <t>1196762821852142</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Elliekeepsbusy with Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+          <t>❤️ 30.000+ Nutzer 💬 4000+ Bewertungen ⭐️ 4,7 Sterne Bewertung</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>⭐️ 4,7 Sterne Bewertung</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Learn More</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1177298251104469</t>
+          <t>3888948801242426</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>709305141982335</t>
+          <t>1373162224393589</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1982848112586220</t>
+          <t>804595359053733</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>leahlongueville with Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Remento is the *only* life story book on Trustpilot with a 4.9 rating. The rest? They just aren't the same...</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>15</v>
+        <v>182</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2529997187363834</t>
+          <t>2393916927736067</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Mach auch deine Oma glücklich &amp; bring die ganze Familie näher zusammen! 🥰 ✅ Erinnerungen &amp; Nachrichten schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Enna</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000311108845016</t>
+          <t>1896813954581984</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>enna.care</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Mit enna bleiben Generationen verbunden: ✅ Erinnerungen schicken ✅ Große Auswahl an Unterhaltung</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Kein Kauf, keine Einrichtung.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9</v>
+        <v>189</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1227220706269158</t>
+          <t>1652739722437976</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>25345822798359945</t>
+          <t>1604340910795794</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kristen Coffield with Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Grandparents don’t need more sweaters or socks or gadgets this holiday! 🙅🎄🎁 For years I kept promising myself I would go through the boxes of photos in the attic. You know, create gift albums to tell the story of our lives. Guess what? That’s probably not going to happen. But what I have started doing is much easier and more impactful.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4079194345667889</t>
+          <t>986777303695569</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1164007795344310</t>
+          <t>830570699644006</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hospice Nursejulie with Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>If you’re looking for the most meaningful holiday gift for a parent, Remento is such a beautiful option. 🎁✨ #ad I used Remento with my mom to turn her memories, stories, and reflections of old photos into a beautiful keepsake - all without her having to do any writing. And what I love most is that I can scan the QR codes inside and actually play the recording used to write each chapter. It's a bit sappy to say, but this is honestly as much of a gift to me. Whether you’re preserving stories, sharing your family history, or helping loved ones reflect… Remento truly makes a gift that becomes a treasure. ❤️</t>
+          <t>Ditch the flowers this Mother's Day! Create a custom book that tells her life story What if you could give her a gift she'll treasure forever?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Turn memories into a lasting keepsake</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>25733276619603138</t>
+          <t>1342635554344428</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2693559387654597</t>
+          <t>792414230413551</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>811494068432964</t>
+          <t>943864791615557</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1223764359659128</t>
+          <t>2181963129245755</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>She has stories you've never even heard. Here's how to finally get them into a book. →</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1935514487281036</t>
+          <t>1680810166448399</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>See why Tim Ferris picked Remento for his mom: "Worked better than could have hoped, A+ investment!" Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. 80% of life story books never get made, because the process requires so much writing &amp; typing. So get Remento and actually make history for your family.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>"My kids see their grandparents as heroes now!"</t>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2903169976739309</t>
+          <t>991000993265523</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1360065051954165</t>
+          <t>1107552519108914</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1407254350467840</t>
+          <t>4209711686009806</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>847636017993619</t>
+          <t>1009981694791489</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Adventures of Amelie &amp; Bros with Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>#ad #RementoPartner When my dad handed me his finished Remento book — filled with a year’s worth of his stories, memories, and parts of his life I never knew — it instantly became one of the most meaningful gifts I’ve ever received. There’s something sacred about holding your parent’s words in your hands… their childhood moments, their dreams, the lessons they learned, the memories they still carry.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>This isn’t just a book — it’s a legacy. And it’s one I’ll treasure forever.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2087429455352258</t>
+          <t>977072525149646</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>Your parents' stories deserve to be remembered - in their own voice, not just on a page. WWW.STORYKEEPER.COM The Only Book That Let's You Listen to Their Story.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>The Only Book That Let's You Listen to Their Story.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Shop Now</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>865773219430251</t>
+          <t>2460360471077841</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+          <t>Your loved one’s stories deserve to be remembered – in their own words and in their own voice. StoryKeeper turns memories into love you can hold and hear. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1935075780755153</t>
+          <t>1660997435024820</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1859686405432155</t>
+          <t>1510732740710867</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>Preserve their stories, and their voice, in a book that lasts generations. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1406850387573556</t>
+          <t>915320794837185</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Actor Cara AnnMarie with Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2264255717420815</t>
+          <t>4327848830865014</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>875217908295393</t>
+          <t>1613608029697579</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mama Blue with Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>@getremento 💙💙💙 #mamabluesunshine #holidaygift #giftguide #giftsforgrandma</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>$99 for 1 Book &amp; 2 Copies</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>878509735060952</t>
+          <t>1531636068580907</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Preserving the stories you love shouldn’t feel like work. With Remento, it’s as easy as talking. No typing. No tech headaches.</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Storykeeper</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3245709482265630</t>
+          <t>1816986676349316</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>StoryKeeper</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Her Story. Bound Forever.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>Keepsake</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>860220086506617</t>
+          <t>1797082684484054</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>frankdenbow with Remento</t>
+          <t>Keepsake Frames</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Highly recommend @getremento for capturing family memories This Book Has Audio &amp; Video Recordings</t>
+          <t>In 5 minutes order your photos printed, framed, and shipped to your doorstep. ITUNES.APPLE.COM Keepsake: Your Photos Printed &amp; Framed</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>This Book Has Audio &amp; Video Recordings</t>
+          <t>Keepsake: Your Photos Printed &amp; Framed</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Install now</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>926057242847548</t>
+          <t>1685628942752739</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Give your grandchildren a gift they can't find anywhere else - your story, in your own words. 80% of life story books never get made, because the process requires so much writing &amp; typing. So get Remento and actually make history for your family. "My kids see their grandparents as heroes now!" - Karen L.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The AI Biographer &amp; Book are only $99!</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1683021615715908</t>
+          <t>1688004719222897</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4140820829505963</t>
+          <t>1657931948555000</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Give your grandchildren a gift they can't find anywhere else - your story, in your own words. 80% of life story books never get made, because the process requires so much writing &amp; typing. So get Remento and actually make history for your family. "My kids see their grandparents as heroes now!" - Karen L.</t>
+          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>The AI Biographer &amp; Book are only $99!</t>
+          <t>✨ Daily check-ins &amp; reminders</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2284784892050208</t>
+          <t>2082672142583809</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>🎁 Win “best gift” this Mother’s Day 🎁 Perfect for every mom with a story to tell – and it’s easy. Gift Mom Remento, not a writing assignment, and her timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>There’s a lot to keep track of. ElliQ helps by sending reminders about appointments, plans, and important moments - and provides company along the way. She makes your life feel simpler and more enjoyable. Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3735,27 +3600,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>26956060197321624</t>
+          <t>952068907735194</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>This Mother's Day, give Mom the ultimate gift: her story. • 80% of life stories never get told because they're too hard to write. Remento makes it easy! Get an interactive book that captures</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>her timeless tales for your whole family.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3764,7 +3634,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3775,2218 +3645,403 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1329644725627223</t>
+          <t>1488992326012147</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
+          <t>A friendly voice. A daily routine. A healthier mind. 💡 ElliQ helps keep minds active and spirits lifted with daily interaction, gentle prompts, and engaging moments that support long-term cognitive health. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1047772133985048</t>
+          <t>1885769545476096</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. "The Most Meaningful Gift I've Ever Given" #1 gift for parents</t>
+          <t>A digital care companion designed for healthy, happy aging at home. Get it free today by your local Area Agency on Aging or your Medicaid provider. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>#1 gift for parents</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shop Now</t>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2119270338888188</t>
+          <t>1682907829804633</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Elliekeepsbusy with Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
+          <t>Conversation, interaction, and mental stimulation are essential for cognitive health 💡 ElliQ helps support healthy aging by providing meaningful daily engagement and companionship. Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>Sorry, we're having trouble playing this video.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Learn more</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>766552155754847</t>
+          <t>2052874168989707</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Let your parents record the story of their journey to America — no writing needed. They ust speak from the heart, and Remento transforms it into a book your family will cherish forever. Their Story is YOUR Story</t>
+          <t>A digital care companion designed for healthy, happy aging at home. Get it at no cost today by the Area Agency on Aging of Broward County. Check you eligibility today at ElliQ.com/free Apply for a free ElliQ today!</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Their Story is YOUR Story</t>
+          <t>Get it free today</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1582636356238641</t>
+          <t>1773179040333547</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
+          <t>Because no one should feel alone. ElliQ is more than technology - she’s a companion who’s there every day to talk, laugh, and brighten your little moments. From sharing stories to telling jokes, ElliQ brings connection, comfort, and smiles right into your home.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
+          <t>✨ A friendly voice</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2132618623933252</t>
+          <t>26725379713817682</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. "The Most Meaningful Gift I've Ever Given" #1 gift for parents</t>
+          <t>Meet ElliQ - the companion designed to support connection, engagement, and independence in your home. It’s more than technology. It’s your companion. Your ElliQ robot can be 100% covered by your insurance plan or your local Area Agency on Aging. Check you eligibility today at ElliQ.com/DSHS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>#1 gift for parents</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Shop Now</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1498264367826187</t>
+          <t>1275450307476970</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>His story is YOUR story too. His favorite gift delivers in seconds ⌛️🎁 Gift Dad Remento, not a writing assignment, and his timeless stories will be captured forever for the whole family in an interactive hardcover book.</t>
+          <t>With ElliQ, getting started takes minutes - not hours. From the moment you plug it in, ElliQ fills your home with meaningful conversation and a sense of connection that fits right into your day. ✨ Plug in and go</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>✨ Daily check-ins &amp; reminders</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2025-06-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1240307351474769</t>
+          <t>2534647506933041</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. "The Most Meaningful Gift I've Ever Given" #1 gift for parents</t>
+          <t>Meet ElliQ - the companion designed to support connection, engagement, and independence in your home. It’s more than technology. It’s your companion. Your ElliQ robot can be 100% covered by your insurance plan or your local Area Agency on Aging. Check you eligibility today at ElliQ.com/free</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>#1 gift for parents</t>
+          <t>Sorry, we're having trouble playing this video.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2025-10-18</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>859529129784224</t>
+          <t>1110969867853136</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hospice Nursejulie with Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>If you’re looking for the most meaningful holiday gift for a parent, Remento is such a beautiful option. 🎁✨ #ad I used Remento with my mom to turn her memories, stories, and reflections of old photos into a beautiful keepsake - all without her having to do any writing. And what I love most is that I can scan the QR codes inside and actually play the recording used to write each chapter. It's a bit sappy to say, but this is honestly as much of a gift to me. Whether you’re preserving stories, sharing your family history, or helping loved ones reflect… Remento truly makes a gift that becomes a treasure. ❤️</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Hospice Nursejulie</t>
+          <t>About one year after she got the robot, Jan went to her doctor for an exam. Her resting heart rate was a few beats lower than before. On some cognitive tests, her short-term memory had improved. She came home and told ElliQ the results. “I’m glad I have you,” Jan said. “Oh, that makes my bells ring,” ElliQ said.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2025-12-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1753342298682872</t>
+          <t>2187179678752035</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remento</t>
+          <t>ElliQ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>See why Mark Cuban invested on Shark Tank: "With Remento, you’ll always have the voices of the people you love.” Give your parent something meaningful… not homework. Remento captures their stories by voice, writes them in their own style, and turns them into a beautiful, interactive, color hardcover book for your entire family.</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>No typing. No passwords. No tech stress.</t>
+          <t>About one year after she got the robot, Jan went to her doctor for an exam. Her resting heart rate was a few beats lower than before. On some cognitive tests, her short-term memory had improved. She came home and told ElliQ the results. “I’m glad I have you,” Jan said. “Oh, that makes my bells ring,” ElliQ said.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="J83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Remento</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1580973983100442</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Remento</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>With Remento, preserving precious stories is as easy as having a conversation. They will simply speak, and Remento will do the rest. Turning their spoken words into professionally written stories. Each story is paired with a QR code that when scanned, links back to original recordings. This way, you can watch or listen to them anytime as they tell their story. 👆 Pick storytelling prompts/photos 📱 Record spoken answers</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>📖 Remento turns recordings into a book of written stories</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>8</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Remento</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1987784852132055</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Remento</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>This Mother's Day, give Mom the ultimate gift: her story. • 80% of life stories never get told because they're too hard to write. Remento makes it easy! Get an interactive book that captures</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>her timeless tales for your whole family.</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>21</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Remento</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1189448479806940</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remento</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>🦈 As seen on Shark Tank, loved by families. Give your parent the gift of a lifetime of stories — without making them write a single sentence. Most life story books never happen. Why?</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Because writing, typing, logins, and tech make it feel like homework.</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>5</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Remento</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1431572054747997</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Remento</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Make history for your family. Give a loved one Remento, not a writing assignment, and their timeless stories will be captured forever for the whole family in an interactive hardcover book. Ad Library APIAbout ads and data usePrivacyTermsCookies Meta © 2026 | English (US)</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Meta © 2026 | English (US)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>40</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Enna</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>890837293883061</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Hennaco Herbs</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Premium export-quality henna, herbal powders, and essential oils supplied directly from trusted sources. Our products are carefully processed, hygienically packed, and quality-tested to meet international standards. We offer reliable wholesale supply, competitive factory prices, and consistent bulk availability for importers, distributors, salons, and private labels worldwide. Timely wholesale delivery and long-term business partnerships guaranteed. Message us today for bulk orders and export inquiries #HennaWholesale #HerbalPowderSupplier #EssentialOilExporter #BulkExport #WholesalePrices #PremiumQuality</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>#B2BSupplier #GlobalDistributors #NaturalProductsExport</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>26507015345657236</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Gift immortality - 🎁 $15 discount until Mother's Day! With Meminto, life stories come alive again! ℹ️ https://meminto.com</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Your story in a book: Meminto makes it possible.</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>16</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2071187966965641</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Want to write a book easily in your browser and get it printed? With Meminto, it’s simple! Sign up now for the free webinar! https://memin.to/webinar</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>What we will cover during the Webinar:</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>823147370601368</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Cherish their memories forever 📚 Give your loved ones a gift that lasts decades, not just moments. Create a personalized book filled with cherished moments, now $69 (reg. $99). Save $30 and start making unforgettable memories today! Your story will stay forever</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Your story will stay forever</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Shop Now</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>7</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1521419769344609</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Create a Lasting Mother's Day Gift 🎁! 52 personal questions to start, customize and expand with our huge database With each answer, your book grows - add pictures, videos or audio recordings too!</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Design the cover &amp; inside pages, we'll print and deliver it to you.</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>9</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>1401225131403742</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Want to write a book easily in your browser and get it printed? With Meminto, it’s simple! Sign up now for the free webinar! https://memin.to/webinar</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>What we will cover during the Webinar:</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>1493133415547667</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Create a Lasting Mother's Day Gift 🎁! 52 personal questions to start, customize and expand with our huge database With each answer, your book grows - add pictures, videos or audio recordings too!</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Design the cover &amp; inside pages, we'll print and deliver it to you.</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>6</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>1271849125125895</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Gift immortality - 🎁 $15 discount until Mother's Day! With Meminto, life stories come alive again! ℹ️ https://meminto.com</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Your story in a book: Meminto makes it possible.</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>4</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1384534506579075</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Give away a Meminto Keepsake with $30 off – start from $69 instead of $99 and give your loved ones a joy that will last for decades. It's simple: 52 questions help capture your entire life story. No typing needed—just speak, and Meminto turns your words into perfect text, placing it in a book. Along with your voice, everything is preserved forever! https://meminto.com/</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>A gift that stays</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>6</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1352201690063216</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Meet "Mum, tell me" - a heartwarming digital way to capture precious moments. Get started with 52 personal questions and customize them as you like from our vast question database. Add pictures 📸, videos, or audio recordings for extra memories</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Design the cover &amp; inside pages just how you want them! ✨ We print it out for you</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>13</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>858552460025860</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>A gift that keeps giving ❤️ Get a printed Meminto Stories book for $69 (reg. $99) and give your loved ones a treasure to cherish for decades. https://meminto.com/</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Your story will stay forever</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>6</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1271171721828353</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Gift immortality - 🎁 $15 discount until Mother's Day! With Meminto, life stories come alive again! ℹ️ https://meminto.com</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Your story in a book: Meminto makes it possible.</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>4</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>1366312008208699</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>A gift that keeps giving: Meminto Stories Receive a printed book with $30 off – start from $69 instead of $99 and give your loved ones a joy that will last for decades. https://meminto.com/</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>A gift that stays</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>6</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>734655232312659</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Cherish their memories forever 📚 Give your loved ones a gift that lasts decades, not just moments. Create a personalized book filled with cherished moments, now $69 (reg. $99). Save $30 and start making unforgettable memories today! Your story will stay forever</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Your story will stay forever</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Learn More</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>6</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1190349616445831</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Create a personalized book for Mum this Mother's Day! 🎁 Get $15 off until the special day and start your digital journey with 52 thought-provoking questions. ✨ Customizable, expandable, and deletable - make it yours! ✨ Add memorable pictures, videos or audio recordings</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>✨ Design every detail of the cover &amp; inside pages</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>5</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1232986075582759</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Create a personalized book for Mum this Mother's Day! 🎁 Get $15 off until the special day and start your digital journey with 52 thought-provoking questions. ✨ Customizable, expandable, and deletable - make it yours! ✨ Add memorable pictures, videos or audio recordings</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>✨ Design every detail of the cover &amp; inside pages</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>15</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1677545886995268</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>🎁 $15 discount until Mother's Day! Like "Mum, tell me" - only DIGITAL! ✨ 52 personal questions await at the beginning ✨ You can customize, expand, delete, or add new ones from our huge question database</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>✨ With each answer, the book grows</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>9</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1546818306474784</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Give away $75 worth for only $9 – a Meminto Stories voucher for a digital book and a AI credits package that makes writing magically easy. You know those fill-in-the-blank books where mom and dad answer questions about life? Each question creates one memory and one story. Meminto turns all these stories into a beautiful book, available digitally or as a printed copy. With this Meminto voucher, you can send a $75 value directly to someone and pay just $9 yourself. It's a generous gift that also saves you money!</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Available for a limited time only!</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Meminto</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>625167363953039</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Meminto Stories</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Give away $75 worth for only $9 – a Meminto Stories voucher for a digital book and a AI credits package that makes writing magically easy. You know those fill-in-the-blank books where mom and dad answer questions about life? Each question creates one memory and one story. Meminto turns all these stories into a beautiful book, available digitally or as a printed copy. With this Meminto voucher, you can send a $75 value directly to someone and pay just $9 yourself. It's a generous gift that also saves you money!</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Available for a limited time only!</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>StoryWorth</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>909728890275547</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Storyworth</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>❤️ Show her that her stories matter ❤️ This Mother's Day, give the mother in your life Storyworth, and their timeless stories will be captured forever. 1️⃣ We send weekly questions about her life.</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>2️⃣ She simply replies by email with a story.</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>40</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>1020039171202528</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>StoryKeeper: Family Book Log</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>👋 Hi everyone, the wait is finally over! We are thrilled to announce that StoryKeeper is now available for both iOS and Android, globally!!! If you've been looking for a simple, convenient way to track reading habits for your kids (without the clutter or ads), we built this for you.</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Free plan includes all needed features:</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>6</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2484750515361769</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Give Mom Her Own Memoir</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I109" t="n">
-        <v>4</v>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>986777303695569</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>11</v>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>1604340910795794</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I111" t="n">
-        <v>11</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>792414230413551</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I112" t="n">
-        <v>11</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1660997435024820</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="I113" t="n">
-        <v>7</v>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>4327848830865014</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="I114" t="n">
-        <v>6</v>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>915320794837185</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I115" t="n">
-        <v>11</v>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>1500578425033379</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="I116" t="n">
-        <v>7</v>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1613608029697579</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>$99 for 1 Book &amp; 2 Copies</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I117" t="n">
-        <v>11</v>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>968456035666410</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Low impression count</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="I118" t="n">
-        <v>10</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>968340959076014</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Low impression count</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="I119" t="n">
-        <v>7</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>1531636068580907</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Low impression count</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I120" t="n">
-        <v>11</v>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>883201354788521</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Low impression count</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
-        <v>6</v>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Storykeeper</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>1521599959561340</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>StoryKeeper</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>This Mother's Day, go beyond flowers! Turn her life story into a keepsake book. What if you could give her a gift that lasts forever?</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Low impression count</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>11</v>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Keepsake</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>1797082684484054</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Keepsake Frames</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>In 5 minutes order your photos printed, framed, and shipped to your doorstep. ITUNES.APPLE.COM Keepsake: Your Photos Printed &amp; Framed</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Keepsake: Your Photos Printed &amp; Framed</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Install now</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="I123" t="n">
-        <v>356</v>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Keepsake</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>907050042180363</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>The Keepsake UK</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>The most unique gift in 2026🎁</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="I124" t="n">
-        <v>65</v>
-      </c>
-      <c r="J124" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6003,7 +4058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -6020,7 +4075,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-12 11:56 UTC</t>
+          <t>Generated: 2026-05-15 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -6039,7 +4094,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -6049,7 +4104,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7"/>
@@ -6063,224 +4118,567 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1020039171202528</t>
+          <t>1009981694791489</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1190349616445831</t>
+          <t>1107552519108914</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1232986075582759</t>
+          <t>1110969867853136</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1271171721828353</t>
+          <t>1171548231746967</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1271849125125895</t>
+          <t>1177236264536592</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1352201690063216</t>
+          <t>1196762821852142</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1485515746687783</t>
+          <t>1275450307476970</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1493133415547667</t>
+          <t>1282383093577411</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1500465744970742</t>
+          <t>1296748252140081</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1500578425033379</t>
+          <t>1342635554344428</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1521419769344609</t>
+          <t>1362684515702149</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1521599959561340</t>
+          <t>1373162224393589</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1531636068580907</t>
+          <t>1488992326012147</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1604340910795794</t>
+          <t>1501005738186114</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1613608029697579</t>
+          <t>1510732740710867</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1660997435024820</t>
+          <t>1531636068580907</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1677545886995268</t>
+          <t>1549478262721918</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1987784852132055</t>
+          <t>1588345672369492</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2284784892050208</t>
+          <t>1604340910795794</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2484750515361769</t>
+          <t>1613608029697579</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26507015345657236</t>
+          <t>1630159098158899</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26956060197321624</t>
+          <t>1639743033742217</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2869974503345418</t>
+          <t>1652739722437976</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4327848830865014</t>
+          <t>1657931948555000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>792414230413551</t>
+          <t>1660997435024820</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>816389671445707</t>
+          <t>1680810166448399</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>883201354788521</t>
+          <t>1682907829804633</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>890837293883061</t>
+          <t>1685628942752739</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>915320794837185</t>
+          <t>1688004719222897</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>968340959076014</t>
+          <t>1701124344229972</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>968456035666410</t>
+          <t>1773179040333547</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>1816986676349316</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1852060685669387</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1868277354563662</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1885769545476096</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1896813954581984</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1938930663325095</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1943193019573119</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1960998354553609</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1985079728773317</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2028325661366433</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2040130603507445</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2052874168989707</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2082672142583809</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2181963129245755</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2187179678752035</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2260190851070799</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2393916927736067</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2460360471077841</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2534647506933041</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>26604726072519208</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>26725379713817682</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2761672647588250</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3727759467519562</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3888948801242426</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3976129939359406</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4072587919646468</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4209711686009806</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4305501549596110</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4327848830865014</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4435145500031851</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4525953724345514</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>792414230413551</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>796404973298946</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>804595359053733</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>830570699644006</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>841302105060560</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>850477457839087</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>852962227868306</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>871339118687590</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>915320794837185</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>933151279692839</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>940930155514923</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>943864791615557</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>944701718393132</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>952068907735194</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>966816482430409</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>977072525149646</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>982542424313716</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>986777303695569</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>991000993265523</t>
         </is>
       </c>
     </row>
